--- a/TestData/T1174_Companies_AddCFOpportunityOnCompanyDetailPage.xlsx
+++ b/TestData/T1174_Companies_AddCFOpportunityOnCompanyDetailPage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SMittal0207\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C1E600-646D-4D1A-8601-0CF00F176223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435A17AF-4633-47DB-83E6-4125F54FFF1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Company" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
   <si>
     <t>CompanyType</t>
   </si>
@@ -146,9 +146,6 @@
     <t>AddOpportunity</t>
   </si>
   <si>
-    <t>Dealership &amp; Rental Services</t>
-  </si>
-  <si>
     <t>Accountant</t>
   </si>
   <si>
@@ -177,6 +174,12 @@
   </si>
   <si>
     <t>Drew Koecher</t>
+  </si>
+  <si>
+    <t>Rob Oudman</t>
+  </si>
+  <si>
+    <t>CSDN-0000006544</t>
   </si>
 </sst>
 </file>
@@ -508,14 +511,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -526,39 +529,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -569,31 +572,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -658,7 +661,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -666,13 +669,13 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -681,7 +684,7 @@
         <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I2" t="s">
         <v>16</v>
@@ -696,10 +699,10 @@
         <v>19</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O2" t="s">
         <v>13</v>
@@ -708,19 +711,19 @@
         <v>11</v>
       </c>
       <c r="Q2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" t="s">
         <v>42</v>
       </c>
-      <c r="R2" t="s">
-        <v>43</v>
-      </c>
       <c r="S2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="T2" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" t="s">
         <v>45</v>
-      </c>
-      <c r="U2" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -732,21 +735,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>49</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/T1174_Companies_AddCFOpportunityOnCompanyDetailPage.xlsx
+++ b/TestData/T1174_Companies_AddCFOpportunityOnCompanyDetailPage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SMittal0207\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19801C17-75D2-4A27-83B8-983D9B5CD8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435A17AF-4633-47DB-83E6-4125F54FFF1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23040" windowHeight="11292" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Company" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
   <si>
     <t>CompanyType</t>
   </si>
@@ -92,6 +92,9 @@
     <t>StdUser</t>
   </si>
   <si>
+    <t>Sector</t>
+  </si>
+  <si>
     <t>Staff</t>
   </si>
   <si>
@@ -170,13 +173,13 @@
     <t>BUS</t>
   </si>
   <si>
-    <t>Ayati Arvind</t>
-  </si>
-  <si>
-    <t>HL Sector ID</t>
-  </si>
-  <si>
-    <t>CSDN-0000001546</t>
+    <t>Drew Koecher</t>
+  </si>
+  <si>
+    <t>Rob Oudman</t>
+  </si>
+  <si>
+    <t>CSDN-0000006544</t>
   </si>
 </sst>
 </file>
@@ -508,14 +511,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -526,39 +529,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -569,36 +572,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>14</v>
@@ -607,34 +610,34 @@
         <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>12</v>
@@ -643,22 +646,22 @@
         <v>10</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -666,13 +669,13 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -681,7 +684,7 @@
         <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I2" t="s">
         <v>16</v>
@@ -696,10 +699,10 @@
         <v>19</v>
       </c>
       <c r="M2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O2" t="s">
         <v>13</v>
@@ -708,19 +711,19 @@
         <v>11</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -732,21 +735,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
